--- a/data/survey_table.xlsx
+++ b/data/survey_table.xlsx
@@ -509,16 +509,18 @@
       <c r="D2" t="n">
         <v>17</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>63 - 70</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3</v>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Универсальный</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Одинаково</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -563,16 +565,18 @@
       <c r="D3" t="n">
         <v>18</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>75+</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2</v>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Атакующий</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ноги</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -613,16 +617,16 @@
       <c r="D4" t="n">
         <v>17</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">до 45 </t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Контратакующий</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Руки</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -667,16 +671,18 @@
       <c r="D5" t="n">
         <v>15</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>50-55</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Контратакующий</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ноги</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -721,16 +727,18 @@
       <c r="D6" t="n">
         <v>15</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>62-68</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Контратакующий</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Руки</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -775,16 +783,18 @@
       <c r="D7" t="n">
         <v>15</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>62-68</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2</v>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Универсальный</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ноги</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -829,16 +839,18 @@
       <c r="D8" t="n">
         <v>16</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>75+</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3</v>
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Универсальный</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Одинаково</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -883,16 +895,18 @@
       <c r="D9" t="n">
         <v>15</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>50-56</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3</v>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Универсальный</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Одинаково</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -933,16 +947,18 @@
       <c r="D10" t="n">
         <v>16</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>50 - 56</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3</v>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Универсальный</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Одинаково</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -987,16 +1003,18 @@
       <c r="D11" t="n">
         <v>16</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>50-56</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>3</v>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Атакующий</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Одинаково</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1037,16 +1055,18 @@
       <c r="D12" t="n">
         <v>17</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>56-62</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Универсальный</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Руки</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1091,16 +1111,18 @@
       <c r="D13" t="n">
         <v>17</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>56-62</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2</v>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Универсальный</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ноги</t>
+        </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1145,16 +1167,18 @@
       <c r="D14" t="n">
         <v>17</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>55-60</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2</v>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Универсальный</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ноги</t>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1199,16 +1223,18 @@
       <c r="D15" t="n">
         <v>21</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>57-63</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2</v>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Универсальный</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ноги</t>
+        </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1249,14 +1275,16 @@
       <c r="D16" t="n">
         <v>17</v>
       </c>
-      <c r="E16" t="n">
-        <v>62</v>
-      </c>
-      <c r="F16" t="n">
-        <v>3</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2</v>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Контратакующий</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ноги</t>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1301,16 +1329,18 @@
       <c r="D17" t="n">
         <v>25</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>68-75</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1</v>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Контратакующий</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Руки</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1355,16 +1385,18 @@
       <c r="D18" t="n">
         <v>25</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>63-70</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3</v>
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Атакующий</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Одинаково</t>
+        </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1409,16 +1441,18 @@
       <c r="D19" t="n">
         <v>23</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>57-63</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>3</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2</v>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Контратакующий</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ноги</t>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
